--- a/output/pdf_financials_xlsx/NAHF.xlsx
+++ b/output/pdf_financials_xlsx/NAHF.xlsx
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>0.12602</v>
       </c>
     </row>
     <row r="125">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>0.12602</v>
       </c>
     </row>
     <row r="126">
@@ -3922,7 +3922,11 @@
           <t>Sub-lease payments (Note 8)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>0.08740000000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/NAHF.xlsx
+++ b/output/pdf_financials_xlsx/NAHF.xlsx
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>1.432439</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.788038</v>
       </c>
     </row>
     <row r="65">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.130974</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.12007</v>
       </c>
     </row>
     <row r="68">
@@ -3332,7 +3332,11 @@
           <t>Net Income (Loss)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>-1.652488</v>
       </c>
